--- a/Documentatie/Nulmetingen/Beroepsproject_Nulmeting.xlsx
+++ b/Documentatie/Nulmetingen/Beroepsproject_Nulmeting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\an123\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsete\Herd\JongerenKansrijker\Documentatie\Nulmetingen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5197A215-B196-4A26-A1AC-817C21775347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FBBC44-C124-423E-947C-DDABD01C20B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{4A5F715F-7E42-4E4C-9AA7-823081137BCA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{4A5F715F-7E42-4E4C-9AA7-823081137BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Nulmeting_PHP_PDO" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="110">
   <si>
     <t>Klas:</t>
   </si>
@@ -1725,7 +1725,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2062,11 +2062,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BD7D3C-5174-4C44-AA3E-844A0D3B84BF}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="78.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="78.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2086,7 +2086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="39.6">
+    <row r="2" spans="1:9" ht="38.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="26.4">
+    <row r="3" spans="1:9" ht="25.5">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="26.4">
+    <row r="4" spans="1:9" ht="25.5">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>11</v>
@@ -2153,7 +2153,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="26.4">
+    <row r="5" spans="1:9" ht="25.5">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>12</v>
@@ -2177,7 +2177,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="26.4">
+    <row r="6" spans="1:9" ht="25.5">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="26.4">
+    <row r="7" spans="1:9" ht="25.5">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>15</v>
@@ -2227,7 +2227,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="26.4">
+    <row r="8" spans="1:9" ht="25.5">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="26.4">
+    <row r="9" spans="1:9" ht="25.5">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>18</v>
@@ -2277,7 +2277,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="26.4">
+    <row r="10" spans="1:9" ht="25.5">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -2301,7 +2301,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="26.4">
+    <row r="11" spans="1:9" ht="25.5">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="26.4">
+    <row r="12" spans="1:9" ht="25.5">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>22</v>
@@ -2351,7 +2351,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="26.4">
+    <row r="13" spans="1:9" ht="25.5">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>23</v>
@@ -2375,7 +2375,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="26.4">
+    <row r="14" spans="1:9" ht="25.5">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
         <v>24</v>
@@ -2399,7 +2399,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="26.4">
+    <row r="15" spans="1:9" ht="25.5">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
         <v>25</v>
@@ -2423,7 +2423,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="26.4">
+    <row r="16" spans="1:9" ht="25.5">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="26.4">
+    <row r="17" spans="1:9" ht="25.5">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>28</v>
@@ -2473,7 +2473,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="26.4">
+    <row r="18" spans="1:9" ht="25.5">
       <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="26.4">
+    <row r="19" spans="1:9" ht="25.5">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
         <v>32</v>
@@ -2523,7 +2523,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="26.4">
+    <row r="20" spans="1:9" ht="25.5">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>33</v>
@@ -2547,7 +2547,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="26.4">
+    <row r="21" spans="1:9" ht="25.5">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
         <v>34</v>
@@ -2571,7 +2571,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="26.4">
+    <row r="22" spans="1:9" ht="25.5">
       <c r="A22" s="1" t="s">
         <v>35</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="26.4">
+    <row r="23" spans="1:9" ht="25.5">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
         <v>37</v>
@@ -2621,7 +2621,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="26.4">
+    <row r="24" spans="1:9" ht="25.5">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
         <v>38</v>
@@ -2645,7 +2645,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="26.4">
+    <row r="25" spans="1:9" ht="25.5">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
         <v>39</v>
@@ -2678,13 +2678,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B9BF60-C9CF-4F50-BD58-A97BDFB90C63}">
   <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" customWidth="1"/>
-    <col min="2" max="2" width="52.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="52.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.6">
+    <row r="1" spans="1:7" ht="30">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="27.6">
+    <row r="2" spans="1:7" ht="29.25">
       <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="27.6">
+    <row r="3" spans="1:7" ht="28.5">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>47</v>
@@ -2751,7 +2751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="27.6">
+    <row r="4" spans="1:7" ht="28.5">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>48</v>
@@ -2772,7 +2772,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="27.6">
+    <row r="5" spans="1:7" ht="28.5">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>49</v>
@@ -2793,7 +2793,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="27.6">
+    <row r="6" spans="1:7" ht="28.5">
       <c r="A6" s="2" t="s">
         <v>51</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" ht="29.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>56</v>
@@ -2881,7 +2881,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="27.6">
+    <row r="10" spans="1:7" ht="28.5">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>57</v>
@@ -2902,7 +2902,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="27.6">
+    <row r="11" spans="1:7" ht="28.5">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>58</v>
@@ -2923,7 +2923,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="27.6">
+    <row r="12" spans="1:7" ht="30">
       <c r="A12" s="2" t="s">
         <v>59</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="27.6">
+    <row r="13" spans="1:7" ht="29.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>62</v>
@@ -2967,7 +2967,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="27.6">
+    <row r="14" spans="1:7" ht="28.5">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>63</v>
@@ -2988,7 +2988,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="27.6">
+    <row r="15" spans="1:7" ht="30">
       <c r="A15" s="2" t="s">
         <v>64</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="27.6">
+    <row r="16" spans="1:7" ht="28.5">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>66</v>
@@ -3032,7 +3032,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="27.6">
+    <row r="17" spans="1:7" ht="28.5">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>67</v>
@@ -3053,7 +3053,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="27.6">
+    <row r="18" spans="1:7" ht="30">
       <c r="A18" s="2" t="s">
         <v>68</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="27.6">
+    <row r="19" spans="1:7" ht="30">
       <c r="A19" s="2" t="s">
         <v>70</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="27.6">
+    <row r="20" spans="1:7" ht="29.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>72</v>
@@ -3120,7 +3120,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="27.6">
+    <row r="21" spans="1:7" ht="29.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>73</v>
@@ -3141,7 +3141,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="27.6">
+    <row r="22" spans="1:7" ht="29.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>74</v>
@@ -3162,7 +3162,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="27.6">
+    <row r="23" spans="1:7" ht="29.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>75</v>
@@ -3183,7 +3183,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="27.6">
+    <row r="24" spans="1:7" ht="30">
       <c r="A24" s="2" t="s">
         <v>76</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="27.6">
+    <row r="25" spans="1:7" ht="28.5">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>78</v>
@@ -3227,7 +3227,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="27.6">
+    <row r="26" spans="1:7" ht="28.5">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>79</v>
@@ -3248,7 +3248,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="27.6">
+    <row r="27" spans="1:7" ht="30">
       <c r="A27" s="2" t="s">
         <v>80</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="27.6">
+    <row r="28" spans="1:7" ht="28.5">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>82</v>
@@ -3292,7 +3292,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="27.6">
+    <row r="29" spans="1:7" ht="28.5">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>83</v>
@@ -3313,7 +3313,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="27.6">
+    <row r="30" spans="1:7" ht="28.5">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>84</v>
@@ -3334,7 +3334,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="27.6">
+    <row r="31" spans="1:7" ht="28.5">
       <c r="A31" s="2" t="s">
         <v>85</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="27.6">
+    <row r="32" spans="1:7" ht="28.5">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>87</v>
@@ -3378,7 +3378,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="27.6">
+    <row r="33" spans="1:7" ht="29.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>88</v>
@@ -3399,7 +3399,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="27.6">
+    <row r="34" spans="1:7" ht="28.5">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>89</v>
@@ -3420,7 +3420,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="27.6">
+    <row r="35" spans="1:7" ht="29.25">
       <c r="A35" s="2" t="s">
         <v>90</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="27.6">
+    <row r="36" spans="1:7" ht="28.5">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>92</v>
@@ -3464,7 +3464,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" ht="28.5">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>93</v>
@@ -3485,7 +3485,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="27.6">
+    <row r="38" spans="1:7" ht="29.25">
       <c r="A38" s="2" t="s">
         <v>94</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="27.6">
+    <row r="39" spans="1:7" ht="28.5">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>96</v>
@@ -3538,11 +3538,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{378E6563-6414-4A58-8B9F-7DC70B186173}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="44.109375" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="44.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3558,6 +3558,9 @@
       <c r="D1" t="s">
         <v>41</v>
       </c>
+      <c r="E1" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="F1" t="s">
         <v>43</v>
       </c>
@@ -3565,7 +3568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="27.6">
+    <row r="2" spans="1:7" ht="30">
       <c r="A2" s="2" t="s">
         <v>97</v>
       </c>
@@ -3578,6 +3581,9 @@
       <c r="D2" t="s">
         <v>46</v>
       </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
       <c r="F2" t="s">
         <v>46</v>
       </c>
@@ -3585,7 +3591,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="27.6">
+    <row r="3" spans="1:7" ht="30">
       <c r="A3" s="3"/>
       <c r="B3" s="5" t="s">
         <v>99</v>
@@ -3596,6 +3602,9 @@
       <c r="D3" t="s">
         <v>46</v>
       </c>
+      <c r="E3" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="F3" t="s">
         <v>46</v>
       </c>
@@ -3603,7 +3612,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="27.6">
+    <row r="4" spans="1:7" ht="30">
       <c r="A4" s="2" t="s">
         <v>100</v>
       </c>
@@ -3616,6 +3625,9 @@
       <c r="D4" t="s">
         <v>46</v>
       </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
       <c r="F4" t="s">
         <v>46</v>
       </c>
@@ -3623,7 +3635,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="27.6">
+    <row r="5" spans="1:7" ht="29.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>102</v>
@@ -3634,6 +3646,9 @@
       <c r="D5" t="s">
         <v>46</v>
       </c>
+      <c r="E5" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="F5" t="s">
         <v>46</v>
       </c>
@@ -3641,7 +3656,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="27.6">
+    <row r="6" spans="1:7" ht="30">
       <c r="A6" s="2" t="s">
         <v>103</v>
       </c>
@@ -3654,6 +3669,9 @@
       <c r="D6" t="s">
         <v>46</v>
       </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
       <c r="F6" t="s">
         <v>46</v>
       </c>
@@ -3661,7 +3679,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="27.6">
+    <row r="7" spans="1:7" ht="29.25">
       <c r="A7" s="3"/>
       <c r="B7" s="5" t="s">
         <v>105</v>
@@ -3672,6 +3690,9 @@
       <c r="D7" t="s">
         <v>46</v>
       </c>
+      <c r="E7" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="F7" t="s">
         <v>46</v>
       </c>
@@ -3679,7 +3700,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="27.6">
+    <row r="8" spans="1:7" ht="30">
       <c r="A8" s="2" t="s">
         <v>106</v>
       </c>
@@ -3692,6 +3713,9 @@
       <c r="D8" t="s">
         <v>50</v>
       </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
       <c r="F8" t="s">
         <v>50</v>
       </c>
@@ -3699,7 +3723,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="27.6">
+    <row r="9" spans="1:7" ht="28.5">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>108</v>
@@ -3710,6 +3734,9 @@
       <c r="D9" t="s">
         <v>109</v>
       </c>
+      <c r="E9" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="F9" t="s">
         <v>50</v>
       </c>
@@ -3719,16 +3746,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="57139c06-7c54-4659-acee-313cb0ba2bf6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3985,17 +4012,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="57139c06-7c54-4659-acee-313cb0ba2bf6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6627DD5E-EAC0-4047-BCD0-64A1396033F2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFB3895D-71BF-42EF-8E3F-8BB416A2D177}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="57139c06-7c54-4659-acee-313cb0ba2bf6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4020,11 +4050,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFB3895D-71BF-42EF-8E3F-8BB416A2D177}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6627DD5E-EAC0-4047-BCD0-64A1396033F2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="57139c06-7c54-4659-acee-313cb0ba2bf6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>